--- a/s04/descargables/S04_ALU_03_Perfil_Alertas_y_Bitacoras.xlsx
+++ b/s04/descargables/S04_ALU_03_Perfil_Alertas_y_Bitacoras.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="176">
   <si>
     <t xml:space="preserve">Perfil transaccional, alertas y bitácoras</t>
   </si>
@@ -68,10 +68,16 @@
     <t xml:space="preserve">L 18 fr. X · RCG 41</t>
   </si>
   <si>
-    <t xml:space="preserve">Presentar el Aviso dentro de las 24 horas siguientes a que se reconozca la sospecha o se conozca el hecho o indicio, aunque el acto no se haya celebrado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L 18 fr. VI 2º párr. · R 7 Bis · RCG 26 Bis, 26 Bis 1 y 26 Bis 2</t>
+    <t xml:space="preserve">Presentar el Aviso dentro de las 24 horas. Son TRES: por sospecha, por hechos o indicios, y por coincidencia con el listado del artículo 38.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L 18 fr. VI 2º párr. · R 7 Bis · RCG 26 Bis, 26 Bis 1 y 27 2º párr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contar con el mecanismo para identificar a las personas publicadas en listas de autoridades nacionales u organismos internacionales, y alertar sobre ellas. NO está diferido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCG 37 Bis fr. IX · RCG 41 fr. V</t>
   </si>
   <si>
     <t xml:space="preserve">Incluir en el Manual los mecanismos para detectar operaciones que se aparten del perfil y para dar seguimiento y acumular.</t>
@@ -107,7 +113,7 @@
     <t xml:space="preserve">1 de marzo de 2027</t>
   </si>
   <si>
-    <t xml:space="preserve">Perfil transaccional, grado de riesgo y política de conocimiento del cliente</t>
+    <t xml:space="preserve">Perfil transaccional, grado de riesgo, política de conocimiento del cliente Y SISTEMA DE ALERTAS</t>
   </si>
   <si>
     <t xml:space="preserve">RCG Trans. Cuarto</t>
@@ -122,6 +128,15 @@
     <t xml:space="preserve">RCG Trans. Noveno</t>
   </si>
   <si>
+    <t xml:space="preserve">Marzo a mayo de 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tres meses en que el sistema de alertas ya es exigible y el mecanismo automatizado todavía no: hay que poder operarlo por otros medios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trans. Cuarto y Noveno leídos juntos</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sin fecha todavía</t>
   </si>
   <si>
@@ -155,6 +170,9 @@
     <t xml:space="preserve">Grado de Riesgo (bajo / medio / alto)</t>
   </si>
   <si>
+    <t xml:space="preserve">Tipo de perfil: inicial declarado por el cliente, o basado en comportamiento observado</t>
+  </si>
+  <si>
     <t xml:space="preserve">1. Monto máximo mensual estimado por el cliente</t>
   </si>
   <si>
@@ -176,6 +194,12 @@
     <t xml:space="preserve">Otras circunstancias relevantes (inciso f)</t>
   </si>
   <si>
+    <t xml:space="preserve">Margen aceptable (% de desviación que NO dispara alerta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por qué ese margen y no otro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fecha del perfil inicial</t>
   </si>
   <si>
@@ -194,6 +218,9 @@
     <t xml:space="preserve">Medio</t>
   </si>
   <si>
+    <t xml:space="preserve">Inicial declarado por el cliente</t>
+  </si>
+  <si>
     <t xml:space="preserve">Querétaro y Guanajuato</t>
   </si>
   <si>
@@ -209,10 +236,13 @@
     <t xml:space="preserve">Opera con una sola contraparte en el extranjero</t>
   </si>
   <si>
+    <t xml:space="preserve">Cubre los meses de temporada alta y el pago adelantado de dos periodos, que es la variación ordinaria observada en el giro</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-11-30</t>
   </si>
   <si>
-    <t xml:space="preserve">Si tuvo que inventar el dato de alguna columna en lugar de tomarlo del expediente, ése es el dato que no le preguntó al cliente en el alta. Métalo al cuestionario de alta esta semana: sin él no hay perfil inicial que sostener. · El cliente con una sola operación también tiene perfil: se integra con la información de ese único acto (RCG 23 Ter 1, último párrafo).</t>
+    <t xml:space="preserve">Si tuvo que inventar el dato de alguna columna en lugar de tomarlo del expediente, ése es el dato que no le preguntó al cliente en el alta. Métalo al cuestionario de alta esta semana: sin él no hay perfil inicial que sostener. · El perfil INICIAL se arma con lo que el propio cliente estime, y el RCG 23 Ter 1 segundo párrafo manda que ese perfil esté incluido en el sistema de alertas, para detectar la inconsistencia entre lo declarado y lo operado: por eso la columna E distingue el perfil declarado del observado. · El cliente con una sola operación también tiene perfil: se integra con la información de ese único acto (RCG 23 Ter 1, último párrafo). · Sobre el margen de la columna M: no está en la norma, es criterio. Lo que sí debe cumplir es estar escrito, tener una razón detrás y aplicarse igual a todos los clientes del mismo grado. Un margen que se ajusta caso por caso para no generar alertas no es un margen.</t>
   </si>
   <si>
     <t xml:space="preserve">Bitácora de alertas</t>
@@ -230,10 +260,16 @@
     <t xml:space="preserve">Cliente</t>
   </si>
   <si>
-    <t xml:space="preserve">¿Por cuál de los cuatro supuestos del RCG 41 fr. V?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qué disparó la alerta</t>
+    <t xml:space="preserve">Grado de Riesgo del cliente EN ESE MOMENTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Por qué se disparó? (desviación del perfil, o uno de los cuatro supuestos del RCG 41 fr. V)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor ESPERADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor OBSERVADO</t>
   </si>
   <si>
     <t xml:space="preserve">Quién la escaló y a quién</t>
@@ -248,6 +284,9 @@
     <t xml:space="preserve">Razón escrita de la resolución</t>
   </si>
   <si>
+    <t xml:space="preserve">Quién analizó</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quién decidió</t>
   </si>
   <si>
@@ -263,22 +302,28 @@
     <t xml:space="preserve">2026-12-03 11:20</t>
   </si>
   <si>
-    <t xml:space="preserve">Grado de Riesgo alto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operación de 3 veces el monto máximo mensual estimado</t>
+    <t xml:space="preserve">Desviación del perfil: el monto del mes supera el máximo estimado más el margen del 20 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$300,000 (estimado $250,000 + margen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$740,000</t>
   </si>
   <si>
     <t xml:space="preserve">Analista de cumplimiento → Representante Encargada de Cumplimiento</t>
   </si>
   <si>
-    <t xml:space="preserve">Expediente, últimos seis meses de operaciones y origen declarado de los recursos</t>
+    <t xml:space="preserve">Expediente, últimos seis meses de operaciones, origen declarado de los recursos y contrapartes</t>
   </si>
   <si>
     <t xml:space="preserve">Actualiza expediente o perfil</t>
   </si>
   <si>
-    <t xml:space="preserve">El cliente abrió una segunda sucursal y su perfil cambió; se recabó el soporte y se ajustó el monto estimado</t>
+    <t xml:space="preserve">El cliente abrió una segunda sucursal y su perfil cambió; se recabó el acta y el contrato de arrendamiento del nuevo local, y se ajustó el monto estimado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analista de cumplimiento</t>
   </si>
   <si>
     <t xml:space="preserve">Representante Encargada de Cumplimiento</t>
@@ -290,7 +335,7 @@
     <t xml:space="preserve">Carpeta 2026 / Alertas / A-2026-001</t>
   </si>
   <si>
-    <t xml:space="preserve">Los cuatro supuestos en que la alerta tiene que sonar (RCG 41 fr. V): 1) Cliente de Grado de Riesgo alto · 2) Persona Políticamente Expuesta · 3) Persona incluida en el listado del RCG 38 · 4) Operación que involucra países o jurisdicciones con régimen fiscal preferente o con medidas deficientes. El cuarto es el que casi nadie tiene configurado. · Una alerta cerrada y documentada es evidencia de control. El año sin una sola alerta es el que se ve mal.</t>
+    <t xml:space="preserve">DOS ALCANCES DISTINTOS QUE CONVIVEN. El RCG 23 Ter 2 impone el sistema de alertas sobre TODOS los clientes y se dispara por desviación del Perfil transaccional. El RCG 41 fr. V es un mínimo ADICIONAL que se dispara por la condición del cliente o de la jurisdicción, aunque la operación sea perfectamente consistente con su perfil: 1) Grado de Riesgo alto · 2) Persona Políticamente Expuesta · 3) Persona del listado del RCG 38 · 4) Países o jurisdicciones con régimen fiscal preferente o con medidas deficientes. El cuarto es el que casi nadie tiene configurado. · Y el RCG 23 Ter 2 nombra DOS delitos: el CPF 400 Bis, que se delata por monto, y el CPF 139 Quáter, que se presenta en importes pequeños y sólo se ve por contraparte, destino y listas. Un catálogo hecho sólo de escenarios de monto cubre la mitad. · Las columnas F y G son las que hacen defendible la bitácora: sin el par esperado/observado la alerta no se puede reconstruir. · Una alerta cerrada y documentada es evidencia de control. El año sin una sola alerta es el que se ve mal.</t>
   </si>
   <si>
     <t xml:space="preserve">Bitácora de operaciones intentadas y no celebradas</t>
@@ -353,7 +398,7 @@
     <t xml:space="preserve">Carpeta 2026 / Intentos / I-2026-004</t>
   </si>
   <si>
-    <t xml:space="preserve">El plazo de 24 horas no corre desde la operación: corre desde que se reconoce la conducta inusitada (RCG 26 Bis) o se conoce el hecho o indicio (RCG 26 Bis 1). Por eso la columna B es el dato más importante de esta hoja. · Al 7 de septiembre de 2026 el envío está diferido hasta que se actualice la Resolución de formatos y transcurran seis meses (R Trans. Quinto y RCG Trans. Quinto). Lo diferido es el envío, no el deber de detectar y documentar.</t>
+    <t xml:space="preserve">El plazo de 24 horas no corre desde la operación: corre desde que se reconoce la conducta inusitada (RCG 26 Bis) o se conoce el hecho o indicio (RCG 26 Bis 1). Por eso la columna B es el dato más importante de esta hoja. · SON TRES AVISOS, no dos: por sospecha (RCG 26 Bis), por hechos o indicios (RCG 26 Bis 1) y por coincidencia con el listado del artículo 38 (RCG 27, segundo párrafo). El RCG 26 Bis 2 no es un cuarto aviso: es la regla de alcance de los tres. · OJO CON LA FUERZA DE CADA SUPUESTO: si el acto NO se celebró, el Aviso «se presentará» (L 18 fr. VI segundo párrafo y R 7 Bis): es deber. Si el acto sí se celebró pero no alcanza el umbral, «se podrán enviar» (RCG 26 Bis 2): es facultad, y se documenta la razón en los dos sentidos. · La negativa o resistencia del cliente a informar sobre el origen de los recursos, la contraparte o el Beneficiario Controlador no es sólo un renglón de esta hoja: es una alerta, y además obliga a abstenerse del acto, sin responsabilidad alguna, conforme al artículo 21 de la Ley. · Al 8 de septiembre de 2026 el envío está diferido hasta que se actualice la Resolución de formatos y transcurran seis meses (R Trans. Quinto y RCG Trans. Quinto). Lo diferido es el envío, no el deber de detectar y documentar, ni el mecanismo de listas del RCG 37 Bis fr. IX.</t>
   </si>
   <si>
     <t xml:space="preserve">Fundamentos citados en este archivo</t>
@@ -513,10 +558,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="0%"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -669,7 +715,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -710,6 +756,10 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -722,7 +772,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -982,7 +1036,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="30"/>
@@ -1199,21 +1253,23 @@
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3"/>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
+      <c r="D17" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>18</v>
-      </c>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="3"/>
@@ -1223,9 +1279,9 @@
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -1236,9 +1292,9 @@
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
     </row>
-    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -1249,9 +1305,9 @@
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1262,8 +1318,10 @@
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3"/>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -1273,10 +1331,8 @@
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>22</v>
-      </c>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="3"/>
@@ -1288,98 +1344,128 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
-      <c r="D24" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
-      <c r="G24" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
     </row>
-    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3"/>
+    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
+      <c r="D28" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
+      <c r="G28" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
+      <c r="D29" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
+      <c r="G29" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
     </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="80">
+  <mergeCells count="86">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A4:C4"/>
@@ -1460,6 +1546,12 @@
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="D29:F29"/>
     <mergeCell ref="G29:I29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1476,25 +1568,28 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1511,7 +1606,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1528,708 +1623,828 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>56</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="8" t="n">
+        <v>63</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="8" t="n">
         <v>250000</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="G7" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>56</v>
-      </c>
       <c r="H7" s="7" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>61</v>
+        <v>68</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>69</v>
       </c>
       <c r="M7" s="9" t="n">
-        <f aca="false">IFERROR(EDATE(L7,6),"")</f>
+        <v>0.2</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="P7" s="10" t="n">
+        <f aca="false">IFERROR(EDATE(O7,6),"")</f>
         <v>46537</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
       <c r="E8" s="11"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L8,6),"")</f>
+      <c r="F8" s="12"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O8,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
       <c r="E9" s="11"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L9,6),"")</f>
+      <c r="F9" s="12"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O9,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
       <c r="E10" s="11"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L10,6),"")</f>
+      <c r="F10" s="12"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O10,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
       <c r="E11" s="11"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L11,6),"")</f>
+      <c r="F11" s="12"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O11,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
       <c r="E12" s="11"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L12,6),"")</f>
+      <c r="F12" s="12"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O12,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
       <c r="E13" s="11"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L13,6),"")</f>
+      <c r="F13" s="12"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O13,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
       <c r="E14" s="11"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L14,6),"")</f>
+      <c r="F14" s="12"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O14,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
       <c r="E15" s="11"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L15,6),"")</f>
+      <c r="F15" s="12"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O15,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
       <c r="E16" s="11"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L16,6),"")</f>
+      <c r="F16" s="12"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O16,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
       <c r="E17" s="11"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L17,6),"")</f>
+      <c r="F17" s="12"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O17,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
       <c r="E18" s="11"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L18,6),"")</f>
+      <c r="F18" s="12"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O18,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
       <c r="E19" s="11"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L19,6),"")</f>
+      <c r="F19" s="12"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="14"/>
+      <c r="P19" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O19,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
       <c r="E20" s="11"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L20,6),"")</f>
+      <c r="F20" s="12"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O20,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
       <c r="E21" s="11"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L21,6),"")</f>
+      <c r="F21" s="12"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O21,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
       <c r="E22" s="11"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L22,6),"")</f>
+      <c r="F22" s="12"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O22,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
       <c r="E23" s="11"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L23,6),"")</f>
+      <c r="F23" s="12"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="14"/>
+      <c r="P23" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O23,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
       <c r="E24" s="11"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L24,6),"")</f>
+      <c r="F24" s="12"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O24,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
       <c r="E25" s="11"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L25,6),"")</f>
+      <c r="F25" s="12"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="14"/>
+      <c r="P25" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O25,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
       <c r="E26" s="11"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L26,6),"")</f>
+      <c r="F26" s="12"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="14"/>
+      <c r="P26" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O26,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
       <c r="E27" s="11"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L27,6),"")</f>
+      <c r="F27" s="12"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="14"/>
+      <c r="P27" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O27,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
       <c r="E28" s="11"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L28,6),"")</f>
+      <c r="F28" s="12"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="14"/>
+      <c r="P28" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O28,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
       <c r="E29" s="11"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L29,6),"")</f>
+      <c r="F29" s="12"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="14"/>
+      <c r="P29" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O29,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
       <c r="E30" s="11"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L30,6),"")</f>
+      <c r="F30" s="12"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="14"/>
+      <c r="P30" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O30,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L31,6),"")</f>
+      <c r="F31" s="12"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="14"/>
+      <c r="P31" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O31,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L32,6),"")</f>
+      <c r="F32" s="12"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="14"/>
+      <c r="P32" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O32,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
       <c r="E33" s="11"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L33,6),"")</f>
+      <c r="F33" s="12"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="14"/>
+      <c r="P33" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O33,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
       <c r="E34" s="11"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L34,6),"")</f>
+      <c r="F34" s="12"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="13"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="14"/>
+      <c r="P34" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O34,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
       <c r="E35" s="11"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L35,6),"")</f>
+      <c r="F35" s="12"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="14"/>
+      <c r="P35" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O35,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
       <c r="E36" s="11"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="12"/>
-      <c r="M36" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L36,6),"")</f>
+      <c r="F36" s="12"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="14"/>
+      <c r="P36" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O36,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
       <c r="E37" s="11"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="12"/>
-      <c r="M37" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L37,6),"")</f>
+      <c r="F37" s="12"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="13"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="14"/>
+      <c r="P37" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O37,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
       <c r="E38" s="11"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="12"/>
-      <c r="M38" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L38,6),"")</f>
+      <c r="F38" s="12"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="13"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="14"/>
+      <c r="P38" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O38,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
+      <c r="A39" s="11"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
       <c r="E39" s="11"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="12"/>
-      <c r="M39" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L39,6),"")</f>
+      <c r="F39" s="12"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="13"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="14"/>
+      <c r="P39" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O39,6),"")</f>
         <v>182</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
+      <c r="A40" s="11"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
       <c r="E40" s="11"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="12"/>
-      <c r="M40" s="13" t="n">
-        <f aca="false">IFERROR(EDATE(L40,6),"")</f>
+      <c r="F40" s="12"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="13"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="14"/>
+      <c r="P40" s="15" t="n">
+        <f aca="false">IFERROR(EDATE(O40,6),"")</f>
         <v>182</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="14"/>
-      <c r="J42" s="14"/>
-      <c r="K42" s="14"/>
-      <c r="L42" s="14"/>
-      <c r="M42" s="14"/>
+    <row r="42" customFormat="false" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
+      <c r="J42" s="16"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+      <c r="M42" s="16"/>
+      <c r="N42" s="16"/>
+      <c r="O42" s="16"/>
+      <c r="P42" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A42:M42"/>
+    <mergeCell ref="A42:P42"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2246,26 +2461,29 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2281,7 +2499,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2297,568 +2515,688 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>86</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>87</v>
+        <v>99</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="11"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="11"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="11"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="11"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10"/>
-      <c r="L33" s="10"/>
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="11"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="11"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="11"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="11"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="11"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="11"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
+      <c r="A39" s="11"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="11"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-    </row>
-    <row r="42" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="14"/>
-      <c r="J42" s="14"/>
-      <c r="K42" s="14"/>
-      <c r="L42" s="14"/>
+      <c r="A40" s="11"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="11"/>
+    </row>
+    <row r="42" customFormat="false" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
+      <c r="J42" s="16"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+      <c r="M42" s="16"/>
+      <c r="N42" s="16"/>
+      <c r="O42" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A42:L42"/>
+    <mergeCell ref="A42:O42"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2893,7 +3231,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2908,7 +3246,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2923,522 +3261,522 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>85</v>
-      </c>
       <c r="J7" s="7" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10"/>
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
+      <c r="A39" s="11"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-    </row>
-    <row r="42" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="14"/>
-      <c r="J42" s="14"/>
-      <c r="K42" s="14"/>
+      <c r="A40" s="11"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+    </row>
+    <row r="42" customFormat="false" ht="43.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
+      <c r="J42" s="16"/>
+      <c r="K42" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3472,7 +3810,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3480,7 +3818,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3488,117 +3826,117 @@
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="D7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="D9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="D13" s="3"/>
     </row>
@@ -3607,10 +3945,10 @@
         <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="D14" s="3"/>
     </row>
@@ -3619,142 +3957,142 @@
         <v>11</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="D22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="D23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="D25" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
+      <c r="A27" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="3">
